--- a/AAII_Financials/Quarterly/CXT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CXT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
   <si>
     <t>CXT</t>
   </si>
@@ -656,314 +656,327 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>493200</v>
+      </c>
+      <c r="E8" s="3">
         <v>387700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>476900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>445100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>404400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>330300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>399100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>403500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>370600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>313600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>356900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>352900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>352400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>329100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>338200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>335100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>334000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>332600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>998500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>833500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>855500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>779500</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>284600</v>
+      </c>
+      <c r="E9" s="3">
         <v>231800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>274700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>252500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>235600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>190100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>218600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>232200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>209700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>161200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>191400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>187400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>184000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>174400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>176900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>174900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>182800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>179100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>663800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>509100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>523500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>470500</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>208600</v>
+      </c>
+      <c r="E10" s="3">
         <v>155900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>202200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>192600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>168800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>140200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>180500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>171300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>160900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>152400</v>
-      </c>
-      <c r="M10" s="3">
-        <v>165500</v>
       </c>
       <c r="N10" s="3">
         <v>165500</v>
       </c>
       <c r="O10" s="3">
+        <v>165500</v>
+      </c>
+      <c r="P10" s="3">
         <v>168400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>154700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>161300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>160200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>151200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>153500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>334700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>324400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>332000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>309000</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,19 +1001,20 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>46000</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1008,11 +1022,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>39500</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1020,11 +1034,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>42800</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1056,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,121 +1141,127 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E14" s="3">
         <v>24100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>10900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>9600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>19700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>11200</v>
-      </c>
-      <c r="J14" s="3">
-        <v>6100</v>
       </c>
       <c r="K14" s="3">
         <v>6100</v>
       </c>
       <c r="L14" s="3">
+        <v>6100</v>
+      </c>
+      <c r="M14" s="3">
         <v>2700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>15200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>6200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-3800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-228700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>6100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-2600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-1100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E15" s="3">
         <v>29700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>28900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>29000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>27100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>21600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>23400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>24700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>20200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>18500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>18600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>20500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>19500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>19000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1260,8 +1283,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>416300</v>
+      </c>
+      <c r="E17" s="3">
         <v>341000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>389000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>353100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>336400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>291900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>321500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>321700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>296200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>254800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>286200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>269800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>267800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>260700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>265200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>257100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>260600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>255700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>884400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>695300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>710900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>639500</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E18" s="3">
         <v>46700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>87900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>92000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>68000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>38400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>77600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>81800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>74400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>58800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>70700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>83100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>84600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>68400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>73000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>78000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>73400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>76900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>114100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>138200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>144600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>140000</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,348 +1478,364 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="L20" s="3">
+        <v>900</v>
+      </c>
+      <c r="M20" s="3">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-700</v>
       </c>
-      <c r="H20" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-600</v>
-      </c>
-      <c r="K20" s="3">
-        <v>900</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>10100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>115500</v>
+      </c>
+      <c r="E21" s="3">
         <v>80800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>109200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>121100</v>
       </c>
-      <c r="G21" s="3">
-        <v>95800</v>
-      </c>
       <c r="H21" s="3">
+        <v>96000</v>
+      </c>
+      <c r="I21" s="3">
         <v>61900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>107500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>107100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>93700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>77200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>93200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>103600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>104500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>88100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>92300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>97800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>86900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>106300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>146000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>169500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>185400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E22" s="3">
         <v>17800</v>
-      </c>
-      <c r="E22" s="3">
-        <v>16200</v>
       </c>
       <c r="F22" s="3">
         <v>16200</v>
       </c>
       <c r="G22" s="3">
+        <v>16200</v>
+      </c>
+      <c r="H22" s="3">
         <v>16400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>13400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>10800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>14100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12900</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>14000</v>
       </c>
       <c r="R22" s="3">
         <v>14000</v>
       </c>
       <c r="S22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="T22" s="3">
         <v>14100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>14200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>10900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>11000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>11400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>13600</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E23" s="3">
         <v>9200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>53500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>66600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>32800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>28100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>61000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>63300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>55400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>46700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>61400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>67900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>55900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>54600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>58900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>64400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>61500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>63500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>105400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>131000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>143300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>130800</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E24" s="3">
         <v>2400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>15700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>16200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>13800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>11900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>16000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>12700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>10900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-3100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>19800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>12700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>14000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-4500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>19600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E26" s="3">
         <v>6800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>47500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>50900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>25000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>21700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>57600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>47100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>41600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>37800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>49500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>51900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>43200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>43700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>62000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>44600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>48800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>49500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>109900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>111400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>138300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>103400</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E27" s="3">
         <v>6400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>48000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>50500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>24900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>21700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>57600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>47100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>41600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>37800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>49500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>51900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>43200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>43700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>62000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>44600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>48800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>49500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>72100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>111400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>138300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>103400</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2101,8 +2162,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -2110,23 +2171,26 @@
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U29" s="3">
         <v>10300</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>3300</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>5200</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>27600</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2328,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>4400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>900</v>
+      </c>
+      <c r="I32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J32" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K32" s="3">
+        <v>600</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N32" s="3">
+        <v>3900</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q32" s="3">
         <v>700</v>
       </c>
-      <c r="H32" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I32" s="3">
-        <v>6500</v>
-      </c>
-      <c r="J32" s="3">
-        <v>600</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>3900</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O32" s="3">
-        <v>400</v>
-      </c>
-      <c r="P32" s="3">
-        <v>700</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-10100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E33" s="3">
         <v>6400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>48000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>50500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>24900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>21700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>57600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>47100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>41600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>37800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>49500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>51900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>43200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>43700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>62000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>44600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>48800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>59800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>75400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>116600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>165900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>108400</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E35" s="3">
         <v>6400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>48000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>50500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>24900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>21700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>57600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>47100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>41600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>37800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>49500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>51900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>43200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>43700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>62000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>44600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>48800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>59800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>75400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>116600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>165900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>108400</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,76 +2744,80 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>231400</v>
+      </c>
+      <c r="E41" s="3">
         <v>228300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>233800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>182400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>152500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>173800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>165800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>165100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>175500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>220600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>227200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>229000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>276900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>218200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>230700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>438600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>650600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>307200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>478600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>450800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>386700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>578400</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2794,291 +2884,306 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>480600</v>
+      </c>
+      <c r="E43" s="3">
         <v>493500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>420600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>368200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>375600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>323200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>312200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>273300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>265000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>224500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>245200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>217800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>233600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>219700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>711600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>572800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>591900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>602600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>569700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>601700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>554600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>578000</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>238500</v>
+      </c>
+      <c r="E44" s="3">
         <v>260500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>169500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>195900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>190300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>158300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>144800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>169800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>171000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>166100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>157100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>165900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>173800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>158700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>145600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>435700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>442900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>471300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>449100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>445800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>456900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>436900</v>
       </c>
     </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E45" s="3">
         <v>28100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>23700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>21500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>23900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>20700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>18900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>20200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>19000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>17900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>35200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>43000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>271200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>266200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>263200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>274100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>49100</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>980500</v>
+      </c>
+      <c r="E46" s="3">
         <v>1014100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>852900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>770600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>743200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>676900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>642500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>630600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>631900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>629100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>644400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>625200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>701200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>609300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>623300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1482300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1728400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1652300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1543100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1761500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1672300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1642400</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E47" s="3">
         <v>8100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>139400</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
@@ -3086,11 +3191,11 @@
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>1300</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
@@ -3107,171 +3212,180 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3">
         <v>400</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
       <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
         <v>51200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>55800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>60000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>62300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>65800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>318400</v>
+      </c>
+      <c r="E48" s="3">
         <v>321200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>371000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>307800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>309500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>276000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>332700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>278000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>271200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>254700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>309000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>244700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>251300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>257900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1512400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>493900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>514200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>516200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>555600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>525800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>538200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>574500</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2181700</v>
+      </c>
+      <c r="E49" s="3">
         <v>2187500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1721200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1734300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1760100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1376800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1375900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1405600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1394000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1127100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1150100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1141600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1160300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1173700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1181900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1917000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1959500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1854800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2050900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1896600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1917300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2098100</v>
       </c>
     </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,76 +3523,82 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>93300</v>
+      </c>
+      <c r="E52" s="3">
         <v>97900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>29400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>103700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>103800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>98300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>31900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>95500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>86700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>85100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>23200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>78500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>77900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>59000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>63000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>239200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>245800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>274100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>277000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>228300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>229600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>201500</v>
       </c>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3665,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3595100</v>
+      </c>
+      <c r="E54" s="3">
         <v>3640400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3116400</v>
-      </c>
-      <c r="F54" s="3">
-        <v>2917700</v>
       </c>
       <c r="G54" s="3">
         <v>2917700</v>
       </c>
       <c r="H54" s="3">
+        <v>2917700</v>
+      </c>
+      <c r="I54" s="3">
         <v>2428700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2386500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2410600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2387500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2098700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2129400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2094100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2195000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2106500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2129400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4132400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4499100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4353200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4486600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4474500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4423200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4586500</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,416 +3792,435 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>118800</v>
+      </c>
+      <c r="E57" s="3">
         <v>130800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>132300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>114700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>104100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>87300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>116600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>108400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>101300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>84100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>106500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>111100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>100800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>96000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>109600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>241100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>247900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>233900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>273700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>244300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>242200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>233600</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>207100</v>
+      </c>
+      <c r="E58" s="3">
         <v>263400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>149700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>261000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>280600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>274600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>220600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>165500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>228100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>38100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>13700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>16100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>315000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>299700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>399500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>119400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>104000</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
       <c r="V58" s="3">
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>15000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>346900</v>
       </c>
     </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>192600</v>
+      </c>
+      <c r="E59" s="3">
         <v>206400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>141300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>104200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>115600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>108700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>102200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>79400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>100100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>100700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>110900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>94300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>108500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>129700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>222100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>435200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>478000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>459900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>560500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>520900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>501600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>454100</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>692800</v>
+      </c>
+      <c r="E60" s="3">
         <v>762700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>569100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>609900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>619100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>563600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>562400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>456400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>526900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>296900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>334400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>312600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>316900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>609200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>631400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1075800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>845300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>797800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>789300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>765200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>758800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1034600</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1260000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1259400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1060000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>834300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>861800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>541100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>593300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>638200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>638900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>639600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>682900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>752200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>873500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>923700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>545100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>843200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>842900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>842700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>842400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>842200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>843400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>843200</v>
       </c>
     </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>98100</v>
+      </c>
+      <c r="E62" s="3">
         <v>110000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>43400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>69300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>69900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>66800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>14000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>77400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>73700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>68500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>21100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>441100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>307800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>502600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>946300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>986500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1180900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1056700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1092900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1110700</v>
       </c>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,76 +4429,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2309300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2381800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1859600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1705200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1741000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1322100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1321600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1339900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1397700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1134600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1165400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1221500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1339800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2106500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1345600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2424100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2637300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2629900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2654300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2666900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2698000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2991500</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,76 +4811,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>395600</v>
+      </c>
+      <c r="E72" s="3">
         <v>370600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>374500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>336300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>295500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>280400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>268400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>220000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>182000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>149600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>120900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>79300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>35300</v>
       </c>
-      <c r="P72" s="3" t="s">
+      <c r="Q72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
       <c r="R72" s="3">
+        <v>0</v>
+      </c>
+      <c r="S72" s="3">
         <v>2752000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2837700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2605900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2527300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2480600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2389300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2276200</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5095,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1266300</v>
+      </c>
+      <c r="E76" s="3">
         <v>1239100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1253000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1214100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1174900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1106600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1064900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1070700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>989800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>964100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>964000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>872600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>855200</v>
       </c>
-      <c r="P76" s="3" t="s">
+      <c r="Q76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>783800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1708300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1861800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1723300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1832300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1807600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1725200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1595000</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E81" s="3">
         <v>6400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>48000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>50500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>24900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>21700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>57600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>47100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>41600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>37800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>49500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>51900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>43200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>43700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>62000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>44600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>48800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>59800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>75400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>116600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>165900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>108400</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,76 +5413,80 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E83" s="3">
         <v>21600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>23400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>24700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>20200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>18500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>18600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>20500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>19500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>19000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>19400</v>
       </c>
       <c r="N83" s="3">
         <v>19400</v>
       </c>
       <c r="O83" s="3">
+        <v>19400</v>
+      </c>
+      <c r="P83" s="3">
         <v>20000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>19900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>29100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>28800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>32400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>28600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>29700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>27500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>30700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>31600</v>
       </c>
     </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5837,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>86700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-14000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>105800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>92000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>62800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-19100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>81100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>66700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>56800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>78500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>102800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>59500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>35500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>75100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>109800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>176600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-55500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>171500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>120300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>156500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>50200</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,76 +5937,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-26400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-10700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-9700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4900</v>
       </c>
     </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6148,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-231200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-126300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-399000</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-13600</v>
       </c>
       <c r="I94" s="3">
         <v>-13600</v>
       </c>
       <c r="J94" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-13300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-278600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-17400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>302200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-13000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-26900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-12100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>9100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>29600</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,40 +6248,41 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E96" s="3">
         <v>10300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>9800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>9700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>9800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>9700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>9200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>9100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>9200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>9100</v>
-      </c>
-      <c r="M96" s="3">
-        <v>7900</v>
       </c>
       <c r="N96" s="3">
         <v>7900</v>
@@ -6056,35 +6290,38 @@
       <c r="O96" s="3">
         <v>7900</v>
       </c>
-      <c r="P96" s="3" t="s">
+      <c r="P96" s="3">
+        <v>7900</v>
+      </c>
+      <c r="Q96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>79500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-79500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>26700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-26700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-25100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-25300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-25200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-25000</v>
       </c>
     </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,208 +6530,220 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-69500</v>
+      </c>
+      <c r="E100" s="3">
         <v>239800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>70300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-51500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>306800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>38000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-53700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-74400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>179600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>10600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-76000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-132800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-46600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-13300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>192200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>24900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-97800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-117100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-35600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-360300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-44900</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E101" s="3">
         <v>6700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-14400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>11900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-7900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>10700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-10300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>14800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-22400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-10300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>14800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-22400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-7500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-5100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-8500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>3000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-7500</v>
       </c>
     </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>51400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>30300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-20900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-9100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-43800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-47900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>58700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>83900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-76900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>343400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-171400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>27800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>64100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-191700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>27400</v>
       </c>
     </row>
